--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/post DFS_HRM-2031-0272/panel_11/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/post DFS_HRM-2031-0272/panel_11/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.76125</v>
+        <v>17.04498</v>
       </c>
       <c r="D2" t="n">
-        <v>16.50335</v>
+        <v>16.62603</v>
       </c>
       <c r="E2" t="n">
-        <v>16.79739</v>
+        <v>16.9204</v>
       </c>
       <c r="F2" t="n">
-        <v>43.25982</v>
+        <v>42.75078</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04974</v>
+        <v>0.0506</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8407</v>
+        <v>1.83206</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.64084</v>
+        <v>17.069</v>
       </c>
       <c r="D3" t="n">
-        <v>16.78925</v>
+        <v>16.52235</v>
       </c>
       <c r="E3" t="n">
-        <v>16.83027</v>
+        <v>16.59103</v>
       </c>
       <c r="F3" t="n">
-        <v>42.7157</v>
+        <v>41.99868</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04996</v>
+        <v>0.05084</v>
       </c>
       <c r="H3" t="n">
-        <v>1.85678</v>
+        <v>1.82146</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.64589</v>
+        <v>16.60432</v>
       </c>
       <c r="D4" t="n">
-        <v>16.75739</v>
+        <v>16.13922</v>
       </c>
       <c r="E4" t="n">
-        <v>16.67862</v>
+        <v>16.49767</v>
       </c>
       <c r="F4" t="n">
-        <v>41.48397</v>
+        <v>43.1121</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05189</v>
+        <v>0.05032</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82307</v>
+        <v>1.81574</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.49804</v>
+        <v>16.57613</v>
       </c>
       <c r="D6" t="n">
-        <v>16.05377</v>
+        <v>15.98341</v>
       </c>
       <c r="E6" t="n">
-        <v>16.38849</v>
+        <v>16.397</v>
       </c>
       <c r="F6" t="n">
-        <v>21.6289</v>
+        <v>21.95943</v>
       </c>
       <c r="G6" t="n">
-        <v>34.01197</v>
+        <v>34.80966</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.40379</v>
+        <v>16.75102</v>
       </c>
       <c r="D7" t="n">
-        <v>16.21983</v>
+        <v>15.97195</v>
       </c>
       <c r="E7" t="n">
-        <v>16.24678</v>
+        <v>16.32281</v>
       </c>
       <c r="F7" t="n">
-        <v>22.16808</v>
+        <v>21.79647</v>
       </c>
       <c r="G7" t="n">
-        <v>34.3425</v>
+        <v>34.30684</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.3505</v>
+        <v>16.72302</v>
       </c>
       <c r="D8" t="n">
-        <v>16.22745</v>
+        <v>16.01786</v>
       </c>
       <c r="E8" t="n">
-        <v>16.53115</v>
+        <v>16.63514</v>
       </c>
       <c r="F8" t="n">
-        <v>21.48893</v>
+        <v>21.97332</v>
       </c>
       <c r="G8" t="n">
-        <v>34.089</v>
+        <v>33.71493</v>
       </c>
     </row>
   </sheetData>
